--- a/DateBase/orders/Nhat 48_2026-9-11.xlsx
+++ b/DateBase/orders/Nhat 48_2026-9-11.xlsx
@@ -529,6 +529,9 @@
       <c r="C11" t="str">
         <v>569_灯笼果_undefined_undefined_1bunch</v>
       </c>
+      <c r="F11" t="str">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -587,7 +590,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>015435631010100</v>
+        <v>015435631010106</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nhat 48_2026-9-11.xlsx
+++ b/DateBase/orders/Nhat 48_2026-9-11.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -533,9 +533,49 @@
         <v>6</v>
       </c>
     </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>622_多丁时尚太子_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F12" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>439_九星叶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F13" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>512_松虫草粉_scabiosa pink_undefined_1bunch</v>
+      </c>
+      <c r="F14" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="str">
+        <v>420_松虫草QQ糖_scabiosa white pink_undefined_1bunch</v>
+      </c>
+      <c r="F15" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>319_尤加利叶带果_Eucalyptus leaves with small pods_undefined_1bunch</v>
+      </c>
+      <c r="F16" t="str">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L16"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -590,7 +630,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>015435631010106</v>
+        <v>015435631010106510555</v>
       </c>
     </row>
   </sheetData>
